--- a/data_static/setores/setores.xlsx
+++ b/data_static/setores/setores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\praia_segura_backend\data_static\setores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68872A8A-8B84-478D-A823-00E30FC4AE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4606C4-FF3D-4775-99CD-FB2E5CDF00AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -357,15 +357,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -696,13 +692,13 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -749,17 +745,17 @@
       <c r="H2">
         <v>-34.875937</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
         <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -799,13 +795,13 @@
       <c r="H3">
         <v>-34.87679</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="3" t="s">
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
         <v>24</v>
       </c>
       <c r="L3" t="s">
@@ -852,13 +848,13 @@
       <c r="H4">
         <v>-34.877769000000001</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" t="s">
         <v>24</v>
       </c>
       <c r="L4" t="s">
@@ -902,13 +898,13 @@
       <c r="H5">
         <v>-34.878708000000003</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="3" t="s">
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" t="s">
         <v>24</v>
       </c>
       <c r="L5" t="s">
@@ -952,17 +948,17 @@
       <c r="H6">
         <v>-34.879660000000001</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="3" t="s">
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
         <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M6" t="s">
         <v>19</v>
@@ -1002,17 +998,17 @@
       <c r="H7">
         <v>-34.880653000000002</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="3" t="s">
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
         <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7" t="s">
         <v>20</v>
@@ -1052,13 +1048,13 @@
       <c r="H8">
         <v>-34.881444000000002</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="3" t="s">
+      <c r="I8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" t="s">
         <v>24</v>
       </c>
       <c r="L8" t="s">
@@ -1105,13 +1101,13 @@
       <c r="H9">
         <v>-34.882250999999997</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" t="s">
         <v>24</v>
       </c>
       <c r="L9" t="s">
@@ -1158,13 +1154,13 @@
       <c r="H10">
         <v>-34.883311999999997</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" t="s">
         <v>24</v>
       </c>
       <c r="L10" t="s">
@@ -1208,13 +1204,13 @@
       <c r="H11">
         <v>-34.884506000000002</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="3" t="s">
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" t="s">
         <v>19</v>
       </c>
       <c r="L11" t="s">
@@ -1258,13 +1254,13 @@
       <c r="H12">
         <v>-34.885731</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="3" t="s">
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" t="s">
         <v>19</v>
       </c>
       <c r="L12" t="s">
@@ -1308,13 +1304,13 @@
       <c r="H13">
         <v>-34.886885999999997</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="3" t="s">
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" t="s">
         <v>19</v>
       </c>
       <c r="L13" t="s">
@@ -1358,13 +1354,13 @@
       <c r="H14">
         <v>-34.888057000000003</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" t="s">
         <v>19</v>
       </c>
       <c r="L14" t="s">
@@ -1408,13 +1404,13 @@
       <c r="H15">
         <v>-34.889324000000002</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" t="s">
         <v>19</v>
       </c>
       <c r="L15" t="s">
@@ -1458,13 +1454,13 @@
       <c r="H16">
         <v>-34.890771000000001</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="3" t="s">
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" t="s">
         <v>19</v>
       </c>
       <c r="L16" t="s">
@@ -1508,17 +1504,17 @@
       <c r="H17">
         <v>-34.892294</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="3" t="s">
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" t="s">
         <v>20</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M17" t="s">
         <v>19</v>
@@ -1558,13 +1554,13 @@
       <c r="H18">
         <v>-34.893711000000003</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="3" t="s">
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" t="s">
         <v>24</v>
       </c>
       <c r="L18" t="s">
@@ -1611,17 +1607,17 @@
       <c r="H19">
         <v>-34.895113000000002</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="3" t="s">
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" t="s">
         <v>61</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" t="s">
         <v>20</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M19" t="s">
         <v>19</v>
@@ -1664,17 +1660,17 @@
       <c r="H20">
         <v>-34.896284000000001</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="I20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" t="s">
         <v>20</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M20" t="s">
         <v>19</v>
@@ -1714,13 +1710,13 @@
       <c r="H21">
         <v>-34.897227000000001</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="3" t="s">
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" t="s">
         <v>24</v>
       </c>
       <c r="L21" t="s">
@@ -1764,13 +1760,13 @@
       <c r="H22">
         <v>-34.898242000000003</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="3" t="s">
+      <c r="I22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" t="s">
         <v>24</v>
       </c>
       <c r="L22" t="s">
@@ -1817,17 +1813,17 @@
       <c r="H23">
         <v>-34.899334000000003</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" t="s">
         <v>61</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="3" t="s">
+      <c r="J23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" t="s">
         <v>20</v>
       </c>
       <c r="L23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M23" t="s">
         <v>19</v>
@@ -1867,17 +1863,17 @@
       <c r="H24">
         <v>-34.900418000000002</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" s="3" t="s">
+      <c r="I24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" t="s">
         <v>20</v>
       </c>
       <c r="L24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M24" t="s">
         <v>19</v>
@@ -1917,17 +1913,17 @@
       <c r="H25">
         <v>-34.901387999999997</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="3" t="s">
+      <c r="I25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" t="s">
         <v>20</v>
       </c>
       <c r="L25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M25" t="s">
         <v>19</v>

--- a/data_static/setores/setores.xlsx
+++ b/data_static/setores/setores.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\praia_segura_backend\data_static\setores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4606C4-FF3D-4775-99CD-FB2E5CDF00AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B55114F-C19A-4231-A48D-55C874148054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="93">
   <si>
     <t>ID_SETOR</t>
   </si>
@@ -97,9 +110,6 @@
     <t xml:space="preserve">nao </t>
   </si>
   <si>
-    <t>quadra de areia</t>
-  </si>
-  <si>
     <t>ID_0003</t>
   </si>
   <si>
@@ -136,9 +146,6 @@
     <t>Pina 4</t>
   </si>
   <si>
-    <t>quadras esportivas/quadra skate</t>
-  </si>
-  <si>
     <t>ID_0009</t>
   </si>
   <si>
@@ -196,9 +203,6 @@
     <t>Acaiaca 2</t>
   </si>
   <si>
-    <t>Volei de praia</t>
-  </si>
-  <si>
     <t>ID_0018</t>
   </si>
   <si>
@@ -208,9 +212,6 @@
     <t xml:space="preserve">sim </t>
   </si>
   <si>
-    <t>Praia sem barreiras (lat: -8.12171; lon: -34.895544)</t>
-  </si>
-  <si>
     <t>ID_0019</t>
   </si>
   <si>
@@ -229,9 +230,6 @@
     <t>Castelinho</t>
   </si>
   <si>
-    <t>Inicio do enroncamento</t>
-  </si>
-  <si>
     <t>ID_0022</t>
   </si>
   <si>
@@ -283,18 +281,12 @@
     <t>Vila militar 1</t>
   </si>
   <si>
-    <t>Quadra de areia</t>
-  </si>
-  <si>
     <t>ID_0030</t>
   </si>
   <si>
     <t>Vila militar 2</t>
   </si>
   <si>
-    <t>Correntes de retorno</t>
-  </si>
-  <si>
     <t>ID_0031</t>
   </si>
   <si>
@@ -302,13 +294,31 @@
   </si>
   <si>
     <t>JAB-80</t>
+  </si>
+  <si>
+    <t>ENRONCAMENTO</t>
+  </si>
+  <si>
+    <t>Mar aberto sem proteção! Banho não é seguro.</t>
+  </si>
+  <si>
+    <t>Piscinas naturais em maré baixa. Não arrisque durante maré alta!</t>
+  </si>
+  <si>
+    <t>Área com correntes de retorno! Banho não é seguro.</t>
+  </si>
+  <si>
+    <t>Piscina natural restrita com correntes de retorno. Banho não é indicado.</t>
+  </si>
+  <si>
+    <t>Sem área de proteção! Banho não é seguro.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +330,25 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -357,16 +386,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -664,14 +762,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.7109375" style="5" customWidth="1"/>
+    <col min="3" max="8" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="3"/>
+    <col min="17" max="17" width="42.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -695,36 +799,39 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C2">
@@ -748,8 +855,8 @@
       <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
-        <v>20</v>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K2" t="s">
         <v>20</v>
@@ -764,17 +871,23 @@
         <v>19</v>
       </c>
       <c r="O2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" t="s">
         <v>21</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R2">
         <v>1.4269000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C3">
@@ -796,39 +909,42 @@
         <v>-34.87679</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
+        <v>19</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
         <v>24</v>
       </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" t="s">
         <v>21</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3">
+        <v>1.1575</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="Q3">
-        <v>1.1575</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
       </c>
       <c r="C4">
         <v>-8.0833010000000005</v>
@@ -849,36 +965,42 @@
         <v>-34.877769000000001</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
+        <v>19</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
         <v>24</v>
       </c>
-      <c r="L4" t="s">
-        <v>20</v>
-      </c>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" t="s">
         <v>21</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="s">
+        <v>92</v>
+      </c>
+      <c r="R4">
         <v>0.84050000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
       </c>
       <c r="C5">
         <v>-8.0859030000000001</v>
@@ -899,36 +1021,42 @@
         <v>-34.878708000000003</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
+        <v>19</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" t="s">
         <v>24</v>
       </c>
-      <c r="L5" t="s">
-        <v>20</v>
-      </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" t="s">
         <v>21</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="s">
+        <v>92</v>
+      </c>
+      <c r="R5">
         <v>0.54269999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
       </c>
       <c r="C6">
         <v>-8.0885060000000006</v>
@@ -951,7 +1079,7 @@
       <c r="I6" t="s">
         <v>20</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K6" t="s">
@@ -964,21 +1092,27 @@
         <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O6" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" t="s">
         <v>21</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="s">
+        <v>89</v>
+      </c>
+      <c r="R6">
         <v>0.26050000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
       </c>
       <c r="C7">
         <v>-8.0910659999999996</v>
@@ -1001,7 +1135,7 @@
       <c r="I7" t="s">
         <v>20</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K7" t="s">
@@ -1017,18 +1151,24 @@
         <v>19</v>
       </c>
       <c r="O7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" t="s">
         <v>21</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="s">
+        <v>89</v>
+      </c>
+      <c r="R7">
         <v>0.15989999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
       </c>
       <c r="C8">
         <v>-8.0936380000000003</v>
@@ -1049,17 +1189,17 @@
         <v>-34.881444000000002</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
+        <v>19</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" t="s">
         <v>24</v>
       </c>
-      <c r="L8" t="s">
-        <v>20</v>
-      </c>
       <c r="M8" t="s">
         <v>20</v>
       </c>
@@ -1067,21 +1207,24 @@
         <v>19</v>
       </c>
       <c r="O8" t="s">
+        <v>19</v>
+      </c>
+      <c r="P8" t="s">
         <v>21</v>
       </c>
-      <c r="P8" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8">
+      <c r="Q8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8">
         <v>0.41170000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
       </c>
       <c r="C9">
         <v>-8.0962560000000003</v>
@@ -1104,11 +1247,11 @@
       <c r="I9" t="s">
         <v>20</v>
       </c>
-      <c r="J9" t="s">
-        <v>19</v>
+      <c r="J9" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s">
         <v>20</v>
@@ -1120,21 +1263,24 @@
         <v>19</v>
       </c>
       <c r="O9" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" t="s">
         <v>21</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
+        <v>91</v>
+      </c>
+      <c r="R9">
+        <v>0.69530000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="Q9">
-        <v>0.69530000000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
       </c>
       <c r="C10">
         <v>-8.0988450000000007</v>
@@ -1157,15 +1303,15 @@
       <c r="I10" t="s">
         <v>20</v>
       </c>
-      <c r="J10" t="s">
-        <v>19</v>
+      <c r="J10" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
         <v>24</v>
       </c>
-      <c r="L10" t="s">
-        <v>20</v>
-      </c>
       <c r="M10" t="s">
         <v>20</v>
       </c>
@@ -1173,18 +1319,24 @@
         <v>19</v>
       </c>
       <c r="O10" t="s">
+        <v>19</v>
+      </c>
+      <c r="P10" t="s">
         <v>21</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="s">
+        <v>90</v>
+      </c>
+      <c r="R10">
         <v>1.0008999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" t="s">
-        <v>42</v>
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C11">
         <v>-8.101324</v>
@@ -1207,14 +1359,14 @@
       <c r="I11" t="s">
         <v>20</v>
       </c>
-      <c r="J11" t="s">
-        <v>19</v>
+      <c r="J11" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K11" t="s">
         <v>19</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
         <v>20</v>
@@ -1223,18 +1375,24 @@
         <v>19</v>
       </c>
       <c r="O11" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" t="s">
         <v>21</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R11">
         <v>1.2984</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="C12">
         <v>-8.1037590000000002</v>
@@ -1257,14 +1415,14 @@
       <c r="I12" t="s">
         <v>20</v>
       </c>
-      <c r="J12" t="s">
-        <v>19</v>
+      <c r="J12" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K12" t="s">
         <v>19</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M12" t="s">
         <v>20</v>
@@ -1273,18 +1431,24 @@
         <v>19</v>
       </c>
       <c r="O12" t="s">
+        <v>19</v>
+      </c>
+      <c r="P12" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>90</v>
+      </c>
+      <c r="R12">
+        <v>1.3495999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="Q12">
-        <v>1.3495999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
       </c>
       <c r="C13">
         <v>-8.1062320000000003</v>
@@ -1307,14 +1471,14 @@
       <c r="I13" t="s">
         <v>20</v>
       </c>
-      <c r="J13" t="s">
-        <v>19</v>
+      <c r="J13" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K13" t="s">
         <v>19</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M13" t="s">
         <v>20</v>
@@ -1323,18 +1487,24 @@
         <v>19</v>
       </c>
       <c r="O13" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13">
+        <v>19</v>
+      </c>
+      <c r="P13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>90</v>
+      </c>
+      <c r="R13">
         <v>1.0492999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C14">
         <v>-8.1086939999999998</v>
@@ -1357,14 +1527,14 @@
       <c r="I14" t="s">
         <v>20</v>
       </c>
-      <c r="J14" t="s">
-        <v>19</v>
+      <c r="J14" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K14" t="s">
         <v>19</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M14" t="s">
         <v>20</v>
@@ -1373,18 +1543,24 @@
         <v>19</v>
       </c>
       <c r="O14" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q14">
+        <v>19</v>
+      </c>
+      <c r="P14" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>90</v>
+      </c>
+      <c r="R14">
         <v>0.75019999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C15">
         <v>-8.1111629999999995</v>
@@ -1407,14 +1583,14 @@
       <c r="I15" t="s">
         <v>20</v>
       </c>
-      <c r="J15" t="s">
-        <v>19</v>
+      <c r="J15" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M15" t="s">
         <v>20</v>
@@ -1423,18 +1599,24 @@
         <v>19</v>
       </c>
       <c r="O15" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q15">
+        <v>19</v>
+      </c>
+      <c r="P15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>90</v>
+      </c>
+      <c r="R15">
         <v>0.44500000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C16">
         <v>-8.1135610000000007</v>
@@ -1457,14 +1639,14 @@
       <c r="I16" t="s">
         <v>20</v>
       </c>
-      <c r="J16" t="s">
-        <v>19</v>
+      <c r="J16" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K16" t="s">
         <v>19</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M16" t="s">
         <v>19</v>
@@ -1473,18 +1655,24 @@
         <v>19</v>
       </c>
       <c r="O16" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q16">
+        <v>19</v>
+      </c>
+      <c r="P16" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>90</v>
+      </c>
+      <c r="R16">
         <v>0.14230000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C17">
         <v>-8.1158020000000004</v>
@@ -1507,7 +1695,7 @@
       <c r="I17" t="s">
         <v>20</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K17" t="s">
@@ -1523,18 +1711,24 @@
         <v>19</v>
       </c>
       <c r="O17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q17">
+        <v>19</v>
+      </c>
+      <c r="P17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>89</v>
+      </c>
+      <c r="R17">
         <v>0.17699999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C18">
         <v>-8.1181280000000005</v>
@@ -1557,15 +1751,15 @@
       <c r="I18" t="s">
         <v>20</v>
       </c>
-      <c r="J18" t="s">
-        <v>19</v>
+      <c r="J18" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" t="s">
         <v>24</v>
       </c>
-      <c r="L18" t="s">
-        <v>20</v>
-      </c>
       <c r="M18" t="s">
         <v>19</v>
       </c>
@@ -1573,21 +1767,24 @@
         <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="P18" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q18">
+        <v>43</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>90</v>
+      </c>
+      <c r="R18">
         <v>0.47099999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C19">
         <v>-8.1204190000000001</v>
@@ -1610,11 +1807,11 @@
       <c r="I19" t="s">
         <v>20</v>
       </c>
-      <c r="J19" t="s">
-        <v>61</v>
+      <c r="J19" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K19" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="L19" t="s">
         <v>20</v>
@@ -1623,24 +1820,27 @@
         <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O19" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="P19" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q19">
+        <v>43</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>89</v>
+      </c>
+      <c r="R19">
         <v>0.77459999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C20">
         <v>-8.1228390000000008</v>
@@ -1661,9 +1861,9 @@
         <v>-34.896284000000001</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K20" t="s">
@@ -1679,18 +1879,24 @@
         <v>19</v>
       </c>
       <c r="O20" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q20">
+        <v>19</v>
+      </c>
+      <c r="P20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>89</v>
+      </c>
+      <c r="R20">
         <v>1.0947</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" t="s">
-        <v>66</v>
+        <v>61</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="C21">
         <v>-8.1255620000000004</v>
@@ -1713,15 +1919,15 @@
       <c r="I21" t="s">
         <v>20</v>
       </c>
-      <c r="J21" t="s">
-        <v>19</v>
+      <c r="J21" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" t="s">
         <v>24</v>
       </c>
-      <c r="L21" t="s">
-        <v>20</v>
-      </c>
       <c r="M21" t="s">
         <v>19</v>
       </c>
@@ -1729,18 +1935,24 @@
         <v>19</v>
       </c>
       <c r="O21" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q21">
+        <v>19</v>
+      </c>
+      <c r="P21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>90</v>
+      </c>
+      <c r="R21">
         <v>1.4056</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="C22">
         <v>-8.1281470000000002</v>
@@ -1763,37 +1975,40 @@
       <c r="I22" t="s">
         <v>20</v>
       </c>
-      <c r="J22" t="s">
-        <v>19</v>
+      <c r="J22" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K22" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" t="s">
         <v>24</v>
       </c>
-      <c r="L22" t="s">
-        <v>20</v>
-      </c>
       <c r="M22" t="s">
         <v>19</v>
       </c>
       <c r="N22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O22" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="P22" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q22">
+        <v>43</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>90</v>
+      </c>
+      <c r="R22">
         <v>1.704</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="C23">
         <v>-8.1306270000000005</v>
@@ -1814,9 +2029,9 @@
         <v>-34.899334000000003</v>
       </c>
       <c r="I23" t="s">
-        <v>61</v>
-      </c>
-      <c r="J23" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K23" t="s">
@@ -1829,21 +2044,27 @@
         <v>19</v>
       </c>
       <c r="N23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O23" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q23">
+        <v>19</v>
+      </c>
+      <c r="P23" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>89</v>
+      </c>
+      <c r="R23">
         <v>1.9992000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="C24">
         <v>-8.1331129999999998</v>
@@ -1866,7 +2087,7 @@
       <c r="I24" t="s">
         <v>19</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K24" t="s">
@@ -1879,21 +2100,27 @@
         <v>19</v>
       </c>
       <c r="N24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q24">
+        <v>19</v>
+      </c>
+      <c r="P24" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>89</v>
+      </c>
+      <c r="R24">
         <v>1.8567</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C25">
         <v>-8.1356350000000006</v>
@@ -1916,8 +2143,8 @@
       <c r="I25" t="s">
         <v>20</v>
       </c>
-      <c r="J25" t="s">
-        <v>20</v>
+      <c r="J25" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K25" t="s">
         <v>20</v>
@@ -1929,21 +2156,27 @@
         <v>19</v>
       </c>
       <c r="N25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O25" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q25">
+        <v>19</v>
+      </c>
+      <c r="P25" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>89</v>
+      </c>
+      <c r="R25">
         <v>1.5459000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C26">
         <v>-8.1382169999999991</v>
@@ -1964,36 +2197,42 @@
         <v>-34.902237999999997</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K26" t="s">
         <v>19</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M26" t="s">
         <v>19</v>
       </c>
       <c r="N26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O26" t="s">
+        <v>19</v>
+      </c>
+      <c r="P26" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>88</v>
+      </c>
+      <c r="R26">
+        <v>1.2497</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>74</v>
       </c>
-      <c r="Q26">
-        <v>1.2497</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
+      <c r="B27" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C27">
         <v>-8.1408109999999994</v>
@@ -2014,36 +2253,42 @@
         <v>-34.903174</v>
       </c>
       <c r="I27" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K27" t="s">
         <v>19</v>
       </c>
       <c r="L27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M27" t="s">
         <v>19</v>
       </c>
       <c r="N27" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="O27" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q27">
+        <v>19</v>
+      </c>
+      <c r="P27" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>88</v>
+      </c>
+      <c r="R27">
         <v>0.95120000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="C28">
         <v>-8.1433319999999991</v>
@@ -2064,36 +2309,42 @@
         <v>-34.904344000000002</v>
       </c>
       <c r="I28" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K28" t="s">
         <v>19</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M28" t="s">
         <v>19</v>
       </c>
       <c r="N28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q28">
+        <v>19</v>
+      </c>
+      <c r="P28" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>88</v>
+      </c>
+      <c r="R28">
         <v>0.64190000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>83</v>
-      </c>
-      <c r="B29" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C29">
         <v>-8.1457529999999991</v>
@@ -2114,36 +2365,42 @@
         <v>-34.90558</v>
       </c>
       <c r="I29" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K29" t="s">
         <v>19</v>
       </c>
       <c r="L29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O29" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q29">
+        <v>19</v>
+      </c>
+      <c r="P29" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>88</v>
+      </c>
+      <c r="R29">
         <v>0.33960000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C30">
         <v>-8.1481750000000002</v>
@@ -2164,16 +2421,16 @@
         <v>-34.906720999999997</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K30" t="s">
         <v>19</v>
       </c>
       <c r="L30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M30" t="s">
         <v>20</v>
@@ -2182,21 +2439,24 @@
         <v>19</v>
       </c>
       <c r="O30" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="P30" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q30">
+        <v>69</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>88</v>
+      </c>
+      <c r="R30">
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C31">
         <v>-8.1506609999999995</v>
@@ -2217,16 +2477,16 @@
         <v>-34.907738999999999</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K31" t="s">
         <v>19</v>
       </c>
       <c r="L31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M31" t="s">
         <v>20</v>
@@ -2235,21 +2495,24 @@
         <v>19</v>
       </c>
       <c r="O31" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="P31" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q31">
+        <v>69</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>88</v>
+      </c>
+      <c r="R31">
         <v>0.25390000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" t="s">
-        <v>92</v>
+        <v>84</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C32">
         <v>-8.1531990000000008</v>
@@ -2270,16 +2533,16 @@
         <v>-34.908681000000001</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" t="s">
-        <v>19</v>
+        <v>19</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="K32" t="s">
         <v>19</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M32" t="s">
         <v>20</v>
@@ -2288,13 +2551,43 @@
         <v>19</v>
       </c>
       <c r="O32" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q32">
+        <v>19</v>
+      </c>
+      <c r="P32" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>88</v>
+      </c>
+      <c r="R32">
         <v>0.33</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I1:J1048576">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="nao">
+      <formula>NOT(ISERROR(SEARCH("nao",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="sim">
+      <formula>NOT(ISERROR(SEARCH("sim",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:L1048576">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="nao">
+      <formula>NOT(ISERROR(SEARCH("nao",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="sim">
+      <formula>NOT(ISERROR(SEARCH("sim",K1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="nao">
+      <formula>NOT(ISERROR(SEARCH("nao",M1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="sim">
+      <formula>NOT(ISERROR(SEARCH("sim",M1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_static/setores/setores.xlsx
+++ b/data_static/setores/setores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\praia_segura_backend\data_static\setores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B55114F-C19A-4231-A48D-55C874148054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D1B439-7DF8-4404-8ABD-6EFD9D1F9A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -403,27 +403,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -915,7 +895,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -971,7 +951,7 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -1027,7 +1007,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -2565,27 +2545,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:J1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="nao">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="nao">
       <formula>NOT(ISERROR(SEARCH("nao",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="sim">
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="sim">
       <formula>NOT(ISERROR(SEARCH("sim",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L1048576">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="nao">
+  <conditionalFormatting sqref="K1:M1048576">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="nao">
       <formula>NOT(ISERROR(SEARCH("nao",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="sim">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="sim">
       <formula>NOT(ISERROR(SEARCH("sim",K1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="nao">
-      <formula>NOT(ISERROR(SEARCH("nao",M1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="sim">
-      <formula>NOT(ISERROR(SEARCH("sim",M1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
